--- a/Teams.xlsx
+++ b/Teams.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Кекс\Downloads\Telegram Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA26264B-E453-455E-96E4-98D7F8FEFC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE3E6AD-01D5-4095-8596-905181004E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ОМО_4" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="130">
   <si>
     <t>#</t>
   </si>
@@ -412,13 +412,19 @@
   </si>
   <si>
     <t>Энкодинги категориальных данных</t>
+  </si>
+  <si>
+    <t>Механизм внимания трансформера</t>
+  </si>
+  <si>
+    <t>Линейный дискриминантный анализ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -427,6 +433,12 @@
     <font>
       <b/>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="6" tint="0.59999389629810485"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -457,12 +469,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -596,7 +609,8 @@
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
     <col min="2" max="2" width="31.28515625" customWidth="1"/>
     <col min="3" max="3" width="14.85546875" customWidth="1"/>
-    <col min="5" max="5" width="63.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="70.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -737,6 +751,9 @@
       <c r="E8" t="s">
         <v>94</v>
       </c>
+      <c r="F8" s="3" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
@@ -754,6 +771,9 @@
       <c r="E9" t="s">
         <v>94</v>
       </c>
+      <c r="F9" s="3" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10">
@@ -771,6 +791,9 @@
       <c r="E10" t="s">
         <v>95</v>
       </c>
+      <c r="F10" s="3" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11">
@@ -788,6 +811,9 @@
       <c r="E11" t="s">
         <v>95</v>
       </c>
+      <c r="F11" s="3" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12">
@@ -1281,6 +1307,9 @@
       <c r="E40" t="s">
         <v>110</v>
       </c>
+      <c r="F40" s="3" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41">
@@ -1297,6 +1326,9 @@
       </c>
       <c r="E41" t="s">
         <v>110</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
@@ -1315,9 +1347,6 @@
       <c r="E42" t="s">
         <v>111</v>
       </c>
-      <c r="F42" t="s">
-        <v>114</v>
-      </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43">
@@ -1335,9 +1364,6 @@
       <c r="E43" t="s">
         <v>111</v>
       </c>
-      <c r="F43" t="s">
-        <v>114</v>
-      </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44">
@@ -1794,6 +1820,9 @@
       <c r="D70">
         <v>35</v>
       </c>
+      <c r="E70" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71">
@@ -1808,6 +1837,9 @@
       <c r="D71">
         <v>35</v>
       </c>
+      <c r="E71" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72">
@@ -1890,6 +1922,9 @@
       <c r="D76">
         <v>38</v>
       </c>
+      <c r="E76" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77">
@@ -1903,6 +1938,9 @@
       </c>
       <c r="D77">
         <v>38</v>
+      </c>
+      <c r="E77" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
